--- a/standards/standard_audit_fields.xlsx
+++ b/standards/standard_audit_fields.xlsx
@@ -13,6 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="APConfig" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SwitchInterfaces" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VlanRoles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SwitchSTP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SwitchMTU" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SwitchDHCPSnooping" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SwitchACL" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SwitchQoS" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -790,6 +795,363 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>org_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>network_id</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>defaultPolicy</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>arpInspection_enabled</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>alerts_email_enabled</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>required_always_allowed_servers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>← required (text format)</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>← optional (blank = org-wide)</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>allow / block</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>True / False  (DAI network-level)</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>True / False  (email alerts on rogue DHCP)</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Comma-sep MACs that must be in alwaysAllowedServers</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>org_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>network_id</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>rule_comment</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>ipVersion</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>srcCidr</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>srcPort</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>dstCidr</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>dstPort</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>vlan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>← required (text format)</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>← optional (blank = org-wide)</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>← required — unique label matching ACL rule comment</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>allow / deny</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>any / ipv4 / ipv6</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>any / tcp / udp</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Source CIDR or 'any'</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Source port or 'any'</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Destination CIDR or 'any'</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>Destination port or 'any'</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="inlineStr">
+        <is>
+          <t>Incoming VLAN or 'any'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="39" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>org_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>network_id</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>rule_name</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>vlan</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>srcPort</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>srcPortRange</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>dstPort</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>dstPortRange</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>dscp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>← required (text format)</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>← optional (blank = org-wide)</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>← required — descriptive label (e.g. VoIP-RTP)</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>VLAN the rule applies to</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>ANY / TCP / UDP</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>Source port number</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>Source port range e.g. 70-80</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
+        <is>
+          <t>Destination port number</t>
+        </is>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Destination port range e.g. 3000-3100</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>DSCP value 0-63 (e.g. 46=EF for voice, 34=AF41 for video)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2118,4 +2480,121 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>org_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>network_id</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>rstpEnabled</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>default_stp_priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>← required (text format)</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>← optional (blank = org-wide)</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>True / False</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Multiple of 4096 e.g. 32768 (0=root, 61440=max)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>org_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>network_id</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>defaultMtuSize</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>← required (text format)</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>← optional (blank = org-wide)</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>e.g. 9578 (jumbo) or 1500</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>